--- a/tests/expedite-eta.xlsx
+++ b/tests/expedite-eta.xlsx
@@ -449,7 +449,7 @@
         <v>EA</v>
       </c>
       <c r="H2" s="1">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>EA</v>
       </c>
       <c r="H3" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="4">
@@ -501,7 +501,7 @@
         <v>EA</v>
       </c>
       <c r="H4" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
         <v>EA</v>
       </c>
       <c r="H5" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="6">
@@ -553,7 +553,7 @@
         <v>EA</v>
       </c>
       <c r="H6" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="7">
@@ -579,7 +579,7 @@
         <v>EA</v>
       </c>
       <c r="H7" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="8">
@@ -605,7 +605,7 @@
         <v>EA</v>
       </c>
       <c r="H8" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="9">
@@ -631,7 +631,7 @@
         <v>EA</v>
       </c>
       <c r="H9" s="1">
-        <v>46292</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="10">
@@ -657,7 +657,7 @@
         <v>EA</v>
       </c>
       <c r="H10" s="1">
-        <v>46347</v>
+        <v>46348</v>
       </c>
     </row>
     <row r="11">
@@ -683,7 +683,7 @@
         <v>EA</v>
       </c>
       <c r="H11" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
   </sheetData>

--- a/tests/expedite-eta.xlsx
+++ b/tests/expedite-eta.xlsx
@@ -449,7 +449,7 @@
         <v>EA</v>
       </c>
       <c r="H2" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>EA</v>
       </c>
       <c r="H3" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="4">
@@ -501,7 +501,7 @@
         <v>EA</v>
       </c>
       <c r="H4" s="1">
-        <v>46233</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
         <v>EA</v>
       </c>
       <c r="H5" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="6">
@@ -553,7 +553,7 @@
         <v>EA</v>
       </c>
       <c r="H6" s="1">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="7">
@@ -579,7 +579,7 @@
         <v>EA</v>
       </c>
       <c r="H7" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="8">
@@ -605,7 +605,7 @@
         <v>EA</v>
       </c>
       <c r="H8" s="1">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="9">
@@ -631,7 +631,7 @@
         <v>EA</v>
       </c>
       <c r="H9" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="10">
@@ -657,7 +657,7 @@
         <v>EA</v>
       </c>
       <c r="H10" s="1">
-        <v>46348</v>
+        <v>46349</v>
       </c>
     </row>
     <row r="11">
@@ -683,7 +683,7 @@
         <v>EA</v>
       </c>
       <c r="H11" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
   </sheetData>

--- a/tests/expedite-eta.xlsx
+++ b/tests/expedite-eta.xlsx
@@ -449,7 +449,7 @@
         <v>EA</v>
       </c>
       <c r="H2" s="1">
-        <v>46259</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>EA</v>
       </c>
       <c r="H3" s="1">
-        <v>46310</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="4">
@@ -501,7 +501,7 @@
         <v>EA</v>
       </c>
       <c r="H4" s="1">
-        <v>46234</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
         <v>EA</v>
       </c>
       <c r="H5" s="1">
-        <v>46303</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="6">
@@ -553,7 +553,7 @@
         <v>EA</v>
       </c>
       <c r="H6" s="1">
-        <v>46249</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="7">
@@ -579,7 +579,7 @@
         <v>EA</v>
       </c>
       <c r="H7" s="1">
-        <v>46303</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="8">
@@ -605,7 +605,7 @@
         <v>EA</v>
       </c>
       <c r="H8" s="1">
-        <v>46249</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="9">
@@ -631,7 +631,7 @@
         <v>EA</v>
       </c>
       <c r="H9" s="1">
-        <v>46294</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="10">
@@ -657,7 +657,7 @@
         <v>EA</v>
       </c>
       <c r="H10" s="1">
-        <v>46349</v>
+        <v>46351</v>
       </c>
     </row>
     <row r="11">
@@ -683,7 +683,7 @@
         <v>EA</v>
       </c>
       <c r="H11" s="1">
-        <v>46303</v>
+        <v>46305</v>
       </c>
     </row>
   </sheetData>

--- a/tests/expedite-eta.xlsx
+++ b/tests/expedite-eta.xlsx
@@ -449,7 +449,7 @@
         <v>EA</v>
       </c>
       <c r="H2" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>EA</v>
       </c>
       <c r="H3" s="1">
-        <v>46312</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="4">
@@ -501,7 +501,7 @@
         <v>EA</v>
       </c>
       <c r="H4" s="1">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
         <v>EA</v>
       </c>
       <c r="H5" s="1">
-        <v>46305</v>
+        <v>46306</v>
       </c>
     </row>
     <row r="6">
@@ -553,7 +553,7 @@
         <v>EA</v>
       </c>
       <c r="H6" s="1">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="7">
@@ -579,7 +579,7 @@
         <v>EA</v>
       </c>
       <c r="H7" s="1">
-        <v>46305</v>
+        <v>46306</v>
       </c>
     </row>
     <row r="8">
@@ -605,7 +605,7 @@
         <v>EA</v>
       </c>
       <c r="H8" s="1">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="9">
@@ -631,7 +631,7 @@
         <v>EA</v>
       </c>
       <c r="H9" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="10">
@@ -657,7 +657,7 @@
         <v>EA</v>
       </c>
       <c r="H10" s="1">
-        <v>46351</v>
+        <v>46352</v>
       </c>
     </row>
     <row r="11">
@@ -683,7 +683,7 @@
         <v>EA</v>
       </c>
       <c r="H11" s="1">
-        <v>46305</v>
+        <v>46306</v>
       </c>
     </row>
   </sheetData>

--- a/tests/expedite-eta.xlsx
+++ b/tests/expedite-eta.xlsx
@@ -449,7 +449,7 @@
         <v>EA</v>
       </c>
       <c r="H2" s="1">
-        <v>46262</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>EA</v>
       </c>
       <c r="H3" s="1">
-        <v>46313</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="4">
@@ -501,7 +501,7 @@
         <v>EA</v>
       </c>
       <c r="H4" s="1">
-        <v>46237</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
         <v>EA</v>
       </c>
       <c r="H5" s="1">
-        <v>46306</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="6">
@@ -553,7 +553,7 @@
         <v>EA</v>
       </c>
       <c r="H6" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="7">
@@ -579,7 +579,7 @@
         <v>EA</v>
       </c>
       <c r="H7" s="1">
-        <v>46306</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="8">
@@ -605,7 +605,7 @@
         <v>EA</v>
       </c>
       <c r="H8" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="9">
@@ -631,7 +631,7 @@
         <v>EA</v>
       </c>
       <c r="H9" s="1">
-        <v>46297</v>
+        <v>46299</v>
       </c>
     </row>
     <row r="10">
@@ -657,7 +657,7 @@
         <v>EA</v>
       </c>
       <c r="H10" s="1">
-        <v>46352</v>
+        <v>46354</v>
       </c>
     </row>
     <row r="11">
@@ -683,7 +683,7 @@
         <v>EA</v>
       </c>
       <c r="H11" s="1">
-        <v>46306</v>
+        <v>46308</v>
       </c>
     </row>
   </sheetData>

--- a/tests/expedite-eta.xlsx
+++ b/tests/expedite-eta.xlsx
@@ -449,7 +449,7 @@
         <v>EA</v>
       </c>
       <c r="H2" s="1">
-        <v>46264</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>EA</v>
       </c>
       <c r="H3" s="1">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="4">
@@ -501,7 +501,7 @@
         <v>EA</v>
       </c>
       <c r="H4" s="1">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
         <v>EA</v>
       </c>
       <c r="H5" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="6">
@@ -553,7 +553,7 @@
         <v>EA</v>
       </c>
       <c r="H6" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="7">
@@ -579,7 +579,7 @@
         <v>EA</v>
       </c>
       <c r="H7" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="8">
@@ -605,7 +605,7 @@
         <v>EA</v>
       </c>
       <c r="H8" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="9">
@@ -631,7 +631,7 @@
         <v>EA</v>
       </c>
       <c r="H9" s="1">
-        <v>46299</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="10">
@@ -657,7 +657,7 @@
         <v>EA</v>
       </c>
       <c r="H10" s="1">
-        <v>46354</v>
+        <v>46355</v>
       </c>
     </row>
     <row r="11">
@@ -683,7 +683,7 @@
         <v>EA</v>
       </c>
       <c r="H11" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
   </sheetData>

--- a/tests/expedite-eta.xlsx
+++ b/tests/expedite-eta.xlsx
@@ -449,7 +449,7 @@
         <v>EA</v>
       </c>
       <c r="H2" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>EA</v>
       </c>
       <c r="H3" s="1">
-        <v>46313</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="4">
@@ -501,7 +501,7 @@
         <v>EA</v>
       </c>
       <c r="H4" s="1">
-        <v>46237</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
         <v>EA</v>
       </c>
       <c r="H5" s="1">
-        <v>46306</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="6">
@@ -553,7 +553,7 @@
         <v>EA</v>
       </c>
       <c r="H6" s="1">
-        <v>46252</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="7">
@@ -579,7 +579,7 @@
         <v>EA</v>
       </c>
       <c r="H7" s="1">
-        <v>46306</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="8">
@@ -605,7 +605,7 @@
         <v>EA</v>
       </c>
       <c r="H8" s="1">
-        <v>46252</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="9">
@@ -631,7 +631,7 @@
         <v>EA</v>
       </c>
       <c r="H9" s="1">
-        <v>46297</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="10">
@@ -657,7 +657,7 @@
         <v>EA</v>
       </c>
       <c r="H10" s="1">
-        <v>46352</v>
+        <v>46355</v>
       </c>
     </row>
     <row r="11">
@@ -683,7 +683,7 @@
         <v>EA</v>
       </c>
       <c r="H11" s="1">
-        <v>46306</v>
+        <v>46309</v>
       </c>
     </row>
   </sheetData>

--- a/tests/expedite-eta.xlsx
+++ b/tests/expedite-eta.xlsx
@@ -449,7 +449,7 @@
         <v>EA</v>
       </c>
       <c r="H2" s="1">
-        <v>46265</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>EA</v>
       </c>
       <c r="H3" s="1">
-        <v>46316</v>
+        <v>46320</v>
       </c>
     </row>
     <row r="4">
@@ -501,7 +501,7 @@
         <v>EA</v>
       </c>
       <c r="H4" s="1">
-        <v>46240</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
         <v>EA</v>
       </c>
       <c r="H5" s="1">
-        <v>46309</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="6">
@@ -553,7 +553,7 @@
         <v>EA</v>
       </c>
       <c r="H6" s="1">
-        <v>46255</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="7">
@@ -579,7 +579,7 @@
         <v>EA</v>
       </c>
       <c r="H7" s="1">
-        <v>46309</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="8">
@@ -605,7 +605,7 @@
         <v>EA</v>
       </c>
       <c r="H8" s="1">
-        <v>46255</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="9">
@@ -631,7 +631,7 @@
         <v>EA</v>
       </c>
       <c r="H9" s="1">
-        <v>46300</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="10">
@@ -657,7 +657,7 @@
         <v>EA</v>
       </c>
       <c r="H10" s="1">
-        <v>46355</v>
+        <v>46359</v>
       </c>
     </row>
     <row r="11">
@@ -683,7 +683,7 @@
         <v>EA</v>
       </c>
       <c r="H11" s="1">
-        <v>46309</v>
+        <v>46313</v>
       </c>
     </row>
   </sheetData>

--- a/tests/expedite-eta.xlsx
+++ b/tests/expedite-eta.xlsx
@@ -449,7 +449,7 @@
         <v>EA</v>
       </c>
       <c r="H2" s="1">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>EA</v>
       </c>
       <c r="H3" s="1">
-        <v>46320</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="4">
@@ -501,7 +501,7 @@
         <v>EA</v>
       </c>
       <c r="H4" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
         <v>EA</v>
       </c>
       <c r="H5" s="1">
-        <v>46313</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="6">
@@ -553,7 +553,7 @@
         <v>EA</v>
       </c>
       <c r="H6" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="7">
@@ -579,7 +579,7 @@
         <v>EA</v>
       </c>
       <c r="H7" s="1">
-        <v>46313</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="8">
@@ -605,7 +605,7 @@
         <v>EA</v>
       </c>
       <c r="H8" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="9">
@@ -631,7 +631,7 @@
         <v>EA</v>
       </c>
       <c r="H9" s="1">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="10">
@@ -657,7 +657,7 @@
         <v>EA</v>
       </c>
       <c r="H10" s="1">
-        <v>46359</v>
+        <v>46360</v>
       </c>
     </row>
     <row r="11">
@@ -683,7 +683,7 @@
         <v>EA</v>
       </c>
       <c r="H11" s="1">
-        <v>46313</v>
+        <v>46314</v>
       </c>
     </row>
   </sheetData>

--- a/tests/expedite-eta.xlsx
+++ b/tests/expedite-eta.xlsx
@@ -449,7 +449,7 @@
         <v>EA</v>
       </c>
       <c r="H2" s="1">
-        <v>46270</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>EA</v>
       </c>
       <c r="H3" s="1">
-        <v>46321</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="4">
@@ -501,7 +501,7 @@
         <v>EA</v>
       </c>
       <c r="H4" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
         <v>EA</v>
       </c>
       <c r="H5" s="1">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="6">
@@ -553,7 +553,7 @@
         <v>EA</v>
       </c>
       <c r="H6" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="7">
@@ -579,7 +579,7 @@
         <v>EA</v>
       </c>
       <c r="H7" s="1">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="8">
@@ -605,7 +605,7 @@
         <v>EA</v>
       </c>
       <c r="H8" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="9">
@@ -631,7 +631,7 @@
         <v>EA</v>
       </c>
       <c r="H9" s="1">
-        <v>46305</v>
+        <v>46306</v>
       </c>
     </row>
     <row r="10">
@@ -657,7 +657,7 @@
         <v>EA</v>
       </c>
       <c r="H10" s="1">
-        <v>46360</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="11">
@@ -683,7 +683,7 @@
         <v>EA</v>
       </c>
       <c r="H11" s="1">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
   </sheetData>

--- a/tests/expedite-eta.xlsx
+++ b/tests/expedite-eta.xlsx
@@ -449,7 +449,7 @@
         <v>EA</v>
       </c>
       <c r="H2" s="1">
-        <v>46271</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>EA</v>
       </c>
       <c r="H3" s="1">
-        <v>46322</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="4">
@@ -501,7 +501,7 @@
         <v>EA</v>
       </c>
       <c r="H4" s="1">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
         <v>EA</v>
       </c>
       <c r="H5" s="1">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="6">
@@ -553,7 +553,7 @@
         <v>EA</v>
       </c>
       <c r="H6" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="7">
@@ -579,7 +579,7 @@
         <v>EA</v>
       </c>
       <c r="H7" s="1">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="8">
@@ -605,7 +605,7 @@
         <v>EA</v>
       </c>
       <c r="H8" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="9">
@@ -631,7 +631,7 @@
         <v>EA</v>
       </c>
       <c r="H9" s="1">
-        <v>46306</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="10">
@@ -657,7 +657,7 @@
         <v>EA</v>
       </c>
       <c r="H10" s="1">
-        <v>46361</v>
+        <v>46362</v>
       </c>
     </row>
     <row r="11">
@@ -683,7 +683,7 @@
         <v>EA</v>
       </c>
       <c r="H11" s="1">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
   </sheetData>
